--- a/backend/signal_logs/signals_2026-08-07.xlsx
+++ b/backend/signal_logs/signals_2026-08-07.xlsx
@@ -662,6 +662,16 @@
           <t>NSE:BSE26AUG3400PE</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:16:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>2026-08-07 06:00:12</t>
@@ -756,6 +766,16 @@
           <t>NSE:JUBLFOOD26AUG475CE</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:17:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>2026-08-07 06:00:12</t>
@@ -850,6 +870,16 @@
           <t>NSE:AUBANK26AUG1080CE</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:00:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2026-08-07 06:00:12</t>
@@ -944,6 +974,16 @@
           <t>NSE:CHOLAFIN26AUG1940CE</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:50:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>2026-08-07 06:00:12</t>
@@ -1038,6 +1078,16 @@
           <t>NSE:BIOCON26AUG435CE</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:15:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026-08-07 06:00:12</t>
@@ -1132,6 +1182,16 @@
           <t>NSE:PNBHOUSING26AUG1140CE</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-08-07 11:07:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-07 06:00:12</t>
@@ -1226,6 +1286,11 @@
           <t>NSE:BANDHANBNK26AUG175PE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed down ~4.6 (-13.0% from entry, EOD estimate)</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>2026-08-07 06:00:12</t>
@@ -1315,6 +1380,11 @@
           <t>NSE:ABB26AUG7700CE</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Closed down ~193.0 (-4.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>2026-08-07 11:06:33</t>
@@ -1622,6 +1692,16 @@
           <t>NSE:BOSCHLTD26AUG42500CE</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:53:00</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-07 09:15:49</t>
@@ -2246,6 +2326,21 @@
           <t>NSE:M&amp;M26AUG3450CE</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:26:00</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:16:00</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Target 2 Hit</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>2026-08-07 10:04:03</t>
@@ -2340,6 +2435,16 @@
           <t>NSE:KAYNES26AUG3900CE</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2026-08-07 13:48:00</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>2026-08-07 09:25:37</t>
@@ -2538,6 +2643,11 @@
           <t>NSE:COFORGE26AUG1800CE</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Closed up ~59.85 (+7.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
           <t>2026-08-07 09:52:20</t>
@@ -2632,6 +2742,16 @@
           <t>NSE:MOTILALOFS26AUG860PE</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:42:00</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
           <t>2026-08-07 09:45:15</t>
@@ -2726,6 +2846,16 @@
           <t>NSE:CROMPTON26AUG250PE</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:58:00</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2815,6 +2945,16 @@
           <t>NSE:MOTILALOFS26AUG860PE</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:42:00</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
           <t>2026-08-07 11:33:13</t>
@@ -3008,6 +3148,16 @@
           <t>NSE:SUZLON26AUG49PE</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-07 15:10:00</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
           <t>2026-08-07 11:13:48</t>
@@ -3102,6 +3252,16 @@
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2026-08-07 11:12:00</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
           <t>2026-08-07 11:20:59</t>
@@ -3493,6 +3653,11 @@
           <t>NSE:JUBLFOOD26AUG480CE</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Closed down ~15.55 (-1.9% from entry)</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
           <t>2026-08-07 11:46:45</t>
@@ -3587,6 +3752,11 @@
           <t>NSE:WAAREEENER26AUG2700PE</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Closed up ~64.3 (+2.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
           <t>2026-08-07 11:52:26</t>
@@ -3681,6 +3851,11 @@
           <t>NSE:ABB26AUG7700CE</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Closed down ~186.9 (-7.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
           <t>2026-08-07 11:58:06</t>
@@ -3879,6 +4054,11 @@
           <t>NSE:JUBLFOOD26AUG480CE</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Closed up ~15.95 (+0.6% from entry)</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
           <t>2026-08-07 12:52:45</t>
@@ -4072,6 +4252,11 @@
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Closed down ~160.0 (-12.8% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4265,6 +4450,11 @@
           <t>NSE:JUBLFOOD26AUG480CE</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Closed up ~16.85 (+6.3% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4354,6 +4544,11 @@
           <t>NSE:BHARATFORG26AUG2260CE</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Closed up ~83.6 (+3.7% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4443,6 +4638,11 @@
           <t>NSE:SONACOMS26AUG820CE</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Closed up ~23.7 (+5.1% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4527,6 +4727,11 @@
           <t>NSE:PGEL26AUG630CE</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Closed up ~23.2 (+1.8% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5857,12 +6062,6 @@
           <t>NSE:M&amp;M26AUG3500CE</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
